--- a/results/method_comparison.xlsx
+++ b/results/method_comparison.xlsx
@@ -586,31 +586,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.18564688628472</v>
+        <v>26.40664011058466</v>
       </c>
       <c r="E2" t="n">
-        <v>1.909816949132093</v>
+        <v>1.590004602121686</v>
       </c>
       <c r="F2" t="n">
         <v>23.79032258064516</v>
       </c>
       <c r="G2" t="n">
-        <v>288.06315625</v>
+        <v>284.11648125</v>
       </c>
       <c r="H2" t="n">
-        <v>8.231175</v>
+        <v>8.153524999999998</v>
       </c>
       <c r="I2" t="n">
-        <v>1.073754023857527</v>
+        <v>1.091212331989247</v>
       </c>
       <c r="J2" t="n">
-        <v>735.26634375</v>
+        <v>739.2130187499999</v>
       </c>
       <c r="K2" t="n">
-        <v>510.8098375</v>
+        <v>527.7454937499999</v>
       </c>
       <c r="L2" t="n">
-        <v>1751.62950696992</v>
+        <v>1843.719535799389</v>
       </c>
       <c r="M2" t="n">
         <v>100</v>
@@ -619,25 +619,25 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2276.348941919024</v>
+        <v>2285.608478850602</v>
       </c>
       <c r="P2" t="n">
-        <v>59.00653225009231</v>
+        <v>58.34547946572953</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.382306115136825</v>
+        <v>2.494165401628202</v>
       </c>
       <c r="S2" t="n">
-        <v>25.21227154040394</v>
+        <v>25.63479065584319</v>
       </c>
       <c r="T2" t="n">
         <v>22.04301075268817</v>
       </c>
       <c r="U2" t="n">
-        <v>1246.07618125</v>
+        <v>1266.9585125</v>
       </c>
       <c r="V2" t="n">
-        <v>71.96786157571857</v>
+        <v>71.45174574135866</v>
       </c>
     </row>
     <row r="3">
@@ -658,28 +658,28 @@
         <v>26.40664011058466</v>
       </c>
       <c r="E3" t="n">
-        <v>1.299232832046734</v>
+        <v>1.205416653616614</v>
       </c>
       <c r="F3" t="n">
-        <v>23.79032258064516</v>
+        <v>23.65591397849462</v>
       </c>
       <c r="G3" t="n">
-        <v>283.93235625</v>
+        <v>283.9348562500001</v>
       </c>
       <c r="H3" t="n">
         <v>8.153524999999998</v>
       </c>
       <c r="I3" t="n">
-        <v>1.103106334005376</v>
+        <v>1.108829527889785</v>
       </c>
       <c r="J3" t="n">
-        <v>739.3971437499999</v>
+        <v>739.39464375</v>
       </c>
       <c r="K3" t="n">
-        <v>536.77875625</v>
+        <v>541.0343124999999</v>
       </c>
       <c r="L3" t="n">
-        <v>1885.399571309875</v>
+        <v>1876.226235997601</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
@@ -688,25 +688,25 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2147.162914250157</v>
+        <v>2341.683398251494</v>
       </c>
       <c r="P3" t="n">
-        <v>57.9384976436242</v>
+        <v>57.74585463261231</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.549914599003853</v>
+        <v>2.537516672398265</v>
       </c>
       <c r="S3" t="n">
-        <v>25.82128910597005</v>
+        <v>25.90734259986161</v>
       </c>
       <c r="T3" t="n">
-        <v>22.04301075268817</v>
+        <v>22.17741935483871</v>
       </c>
       <c r="U3" t="n">
-        <v>1276.1759</v>
+        <v>1280.42895625</v>
       </c>
       <c r="V3" t="n">
-        <v>70.88966389742981</v>
+        <v>70.83010652977802</v>
       </c>
     </row>
     <row r="4">
@@ -727,7 +727,7 @@
         <v>26.40664011058466</v>
       </c>
       <c r="E4" t="n">
-        <v>1.348850403213068</v>
+        <v>1.197109418008952</v>
       </c>
       <c r="F4" t="n">
         <v>23.65591397849462</v>
@@ -739,16 +739,16 @@
         <v>8.153524999999998</v>
       </c>
       <c r="I4" t="n">
-        <v>1.101205922379032</v>
+        <v>1.108692372311828</v>
       </c>
       <c r="J4" t="n">
         <v>739.6391</v>
       </c>
       <c r="K4" t="n">
-        <v>535.60680625</v>
+        <v>541.176725</v>
       </c>
       <c r="L4" t="n">
-        <v>1879.285908242032</v>
+        <v>1876.33190745596</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
@@ -757,25 +757,25 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2250.094910752281</v>
+        <v>2344.59300145251</v>
       </c>
       <c r="P4" t="n">
-        <v>57.99972353371356</v>
+        <v>57.7474985523387</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.540814713881448</v>
+        <v>2.536820873120364</v>
       </c>
       <c r="S4" t="n">
-        <v>25.80247223481186</v>
+        <v>25.91517024324511</v>
       </c>
       <c r="T4" t="n">
         <v>22.17741935483871</v>
       </c>
       <c r="U4" t="n">
-        <v>1275.24590625</v>
+        <v>1280.815825</v>
       </c>
       <c r="V4" t="n">
-        <v>71.10122020828875</v>
+        <v>70.82779836827828</v>
       </c>
     </row>
     <row r="5">
@@ -793,49 +793,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26.42865138790538</v>
+        <v>23.34944528885896</v>
       </c>
       <c r="E5" t="n">
-        <v>16.91267188022946</v>
+        <v>14.05693888683988</v>
       </c>
       <c r="F5" t="n">
-        <v>26.61290322580645</v>
+        <v>28.36021505376344</v>
       </c>
       <c r="G5" t="n">
-        <v>263.939575</v>
+        <v>328.9534857142857</v>
       </c>
       <c r="H5" t="n">
-        <v>8.182000000000002</v>
+        <v>9.775675</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4293719422043011</v>
+        <v>0.5806249615975423</v>
       </c>
       <c r="J5" t="n">
-        <v>717.2880250000001</v>
+        <v>659.27585</v>
       </c>
       <c r="K5" t="n">
-        <v>99.738625</v>
+        <v>156.7389142857143</v>
       </c>
       <c r="L5" t="n">
-        <v>1117.575425795201</v>
+        <v>1100.166276861463</v>
       </c>
       <c r="M5" t="n">
-        <v>2.469135802469136</v>
+        <v>44.55958549222798</v>
       </c>
       <c r="N5" t="n">
-        <v>2.023121387283237</v>
+        <v>11.56862745098039</v>
       </c>
       <c r="O5" t="n">
-        <v>-76.63265444990111</v>
+        <v>-99.58202783533511</v>
       </c>
       <c r="P5" t="n">
-        <v>87.79248816424777</v>
+        <v>80.79214725692944</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.558056717585939</v>
+        <v>1.668749548252773</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -853,49 +853,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25.66524997893208</v>
+        <v>26.7994785213956</v>
       </c>
       <c r="E6" t="n">
-        <v>16.43697666219747</v>
+        <v>15.97369446048375</v>
       </c>
       <c r="F6" t="n">
-        <v>26.20967741935484</v>
+        <v>25.67204301075269</v>
       </c>
       <c r="G6" t="n">
-        <v>260.288175</v>
+        <v>245.8346464285715</v>
       </c>
       <c r="H6" t="n">
-        <v>7.7394</v>
+        <v>8.261150000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4116069220430107</v>
+        <v>0.5120759984639017</v>
       </c>
       <c r="J6" t="n">
-        <v>727.1259499999999</v>
+        <v>745.3666928571428</v>
       </c>
       <c r="K6" t="n">
-        <v>88.30302500000002</v>
+        <v>182.4132607142857</v>
       </c>
       <c r="L6" t="n">
-        <v>1407.646797365715</v>
+        <v>1134.257271086604</v>
       </c>
       <c r="M6" t="n">
-        <v>11.51960784313725</v>
+        <v>43.95886889460154</v>
       </c>
       <c r="N6" t="n">
-        <v>8.136482939632545</v>
+        <v>10.03861003861004</v>
       </c>
       <c r="O6" t="n">
-        <v>-306.4842834242099</v>
+        <v>142.552014153365</v>
       </c>
       <c r="P6" t="n">
-        <v>89.17097286124766</v>
+        <v>80.3387365708757</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.935905048314828</v>
+        <v>1.521743971063108</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -913,49 +913,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>26.47166771272644</v>
+        <v>22.39798671381331</v>
       </c>
       <c r="E7" t="n">
-        <v>16.8843705053516</v>
+        <v>12.18235560626872</v>
       </c>
       <c r="F7" t="n">
-        <v>24.86559139784946</v>
+        <v>29.97311827956989</v>
       </c>
       <c r="G7" t="n">
-        <v>259.298075</v>
+        <v>323.3304142857143</v>
       </c>
       <c r="H7" t="n">
-        <v>9.009125000000001</v>
+        <v>8.247425</v>
       </c>
       <c r="I7" t="n">
-        <v>0.473146001344086</v>
+        <v>0.5768867895545315</v>
       </c>
       <c r="J7" t="n">
-        <v>719.5371499999999</v>
+        <v>681.5153071428571</v>
       </c>
       <c r="K7" t="n">
-        <v>140.1143</v>
+        <v>135.8011035714286</v>
       </c>
       <c r="L7" t="n">
-        <v>1363.905366099601</v>
+        <v>1490.078742722848</v>
       </c>
       <c r="M7" t="n">
-        <v>19.559902200489</v>
+        <v>31.18556701030928</v>
       </c>
       <c r="N7" t="n">
-        <v>6.796116504854369</v>
+        <v>5.387931034482759</v>
       </c>
       <c r="O7" t="n">
-        <v>23.9888318101639</v>
+        <v>-50.20651667840389</v>
       </c>
       <c r="P7" t="n">
-        <v>83.70103371546689</v>
+        <v>83.38451280419702</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.895531545660431</v>
+        <v>2.186420065852611</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -973,31 +973,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>23.96605161480412</v>
+        <v>24.27485485847447</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8182151986371745</v>
+        <v>-1.056371017032824</v>
       </c>
       <c r="F8" t="n">
-        <v>16.8010752688172</v>
+        <v>16.26344086021505</v>
       </c>
       <c r="G8" t="n">
-        <v>191.48985625</v>
+        <v>186.8098875</v>
       </c>
       <c r="H8" t="n">
-        <v>6.685587499999999</v>
+        <v>6.602374999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>1.069427234543011</v>
+        <v>1.086066633064516</v>
       </c>
       <c r="J8" t="n">
-        <v>606.09514375</v>
+        <v>610.7751125</v>
       </c>
       <c r="K8" t="n">
-        <v>604.1640062500001</v>
+        <v>621.2236875</v>
       </c>
       <c r="L8" t="n">
-        <v>2070.310236121836</v>
+        <v>2201.616662105195</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
@@ -1006,25 +1006,25 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1104.185327845351</v>
+        <v>1050.604466430742</v>
       </c>
       <c r="P8" t="n">
-        <v>50.0797819830571</v>
+        <v>49.57595027689963</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.415817231783976</v>
+        <v>3.6046273285328</v>
       </c>
       <c r="S8" t="n">
-        <v>25.08529297856505</v>
+        <v>25.53589522313513</v>
       </c>
       <c r="T8" t="n">
-        <v>28.22580645161291</v>
+        <v>28.76344086021506</v>
       </c>
       <c r="U8" t="n">
-        <v>1210.25915</v>
+        <v>1231.9988</v>
       </c>
       <c r="V8" t="n">
-        <v>67.31888321191374</v>
+        <v>66.83003668510067</v>
       </c>
     </row>
     <row r="9">
@@ -1045,28 +1045,28 @@
         <v>24.27485485847447</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.407794995259031</v>
+        <v>-1.488838182903368</v>
       </c>
       <c r="F9" t="n">
         <v>16.26344086021505</v>
       </c>
       <c r="G9" t="n">
-        <v>187.29615625</v>
+        <v>186.8582625</v>
       </c>
       <c r="H9" t="n">
         <v>6.602374999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>1.104456384408602</v>
+        <v>1.106519665658602</v>
       </c>
       <c r="J9" t="n">
-        <v>610.28884375</v>
+        <v>610.7267375</v>
       </c>
       <c r="K9" t="n">
-        <v>634.4193937499999</v>
+        <v>636.3923687500001</v>
       </c>
       <c r="L9" t="n">
-        <v>2227.609443021797</v>
+        <v>2243.022792875625</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
@@ -1075,25 +1075,25 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1013.913170376641</v>
+        <v>1080.941745224375</v>
       </c>
       <c r="P9" t="n">
-        <v>49.03067444751284</v>
+        <v>48.97100320565312</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.65009038889513</v>
+        <v>3.672710977183351</v>
       </c>
       <c r="S9" t="n">
-        <v>25.79932637610784</v>
+        <v>25.84929695383626</v>
       </c>
       <c r="T9" t="n">
         <v>28.76344086021506</v>
       </c>
       <c r="U9" t="n">
-        <v>1244.7082375</v>
+        <v>1247.11910625</v>
       </c>
       <c r="V9" t="n">
-        <v>66.40120904237206</v>
+        <v>66.3079579452959</v>
       </c>
     </row>
     <row r="10">
@@ -1114,28 +1114,28 @@
         <v>24.27485485847447</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.321373351982237</v>
+        <v>-1.490352437976927</v>
       </c>
       <c r="F10" t="n">
         <v>16.26344086021505</v>
       </c>
       <c r="G10" t="n">
-        <v>186.9453875</v>
+        <v>186.768075</v>
       </c>
       <c r="H10" t="n">
         <v>6.602374999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>1.099538608870968</v>
+        <v>1.106389944556452</v>
       </c>
       <c r="J10" t="n">
-        <v>610.6396124999999</v>
+        <v>610.816925</v>
       </c>
       <c r="K10" t="n">
-        <v>631.1113375</v>
+        <v>636.38604375</v>
       </c>
       <c r="L10" t="n">
-        <v>2221.265868599063</v>
+        <v>2243.196594818203</v>
       </c>
       <c r="M10" t="n">
         <v>100</v>
@@ -1144,25 +1144,25 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1028.356031119687</v>
+        <v>1081.045224033359</v>
       </c>
       <c r="P10" t="n">
-        <v>49.17569118831759</v>
+        <v>48.97494155359387</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.637605263610479</v>
+        <v>3.672453239271658</v>
       </c>
       <c r="S10" t="n">
-        <v>25.73803006336411</v>
+        <v>25.85103518930626</v>
       </c>
       <c r="T10" t="n">
         <v>28.76344086021506</v>
       </c>
       <c r="U10" t="n">
-        <v>1241.75095</v>
+        <v>1247.20296875</v>
       </c>
       <c r="V10" t="n">
-        <v>66.58759451724197</v>
+        <v>66.31073054844346</v>
       </c>
     </row>
     <row r="11">
@@ -1180,49 +1180,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>24.47193260879757</v>
+        <v>20.93104187173977</v>
       </c>
       <c r="E11" t="n">
-        <v>15.81779486662763</v>
+        <v>11.42777834052015</v>
       </c>
       <c r="F11" t="n">
-        <v>22.04301075268817</v>
+        <v>20.43010752688172</v>
       </c>
       <c r="G11" t="n">
-        <v>194.2516000000001</v>
+        <v>221.119275</v>
       </c>
       <c r="H11" t="n">
-        <v>5.338825</v>
+        <v>6.004425000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3566331653225808</v>
+        <v>0.5045465581797236</v>
       </c>
       <c r="J11" t="n">
-        <v>578.7723999999999</v>
+        <v>542.0363357142857</v>
       </c>
       <c r="K11" t="n">
-        <v>96.55272500000001</v>
+        <v>197.2056214285714</v>
       </c>
       <c r="L11" t="n">
-        <v>733.4051415202343</v>
+        <v>774.5008374902231</v>
       </c>
       <c r="M11" t="n">
-        <v>1.449275362318841</v>
+        <v>54.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.492537313432836</v>
+        <v>16.48550724637681</v>
       </c>
       <c r="O11" t="n">
-        <v>152.0472978610156</v>
+        <v>-79.78653222058028</v>
       </c>
       <c r="P11" t="n">
-        <v>85.7027790873322</v>
+        <v>73.32326452481622</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.267173661909646</v>
+        <v>1.428872543147131</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -1240,49 +1240,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>26.27181475454845</v>
+        <v>27.30342016474724</v>
       </c>
       <c r="E12" t="n">
-        <v>17.71300817523483</v>
+        <v>16.18130030491545</v>
       </c>
       <c r="F12" t="n">
-        <v>19.48924731182796</v>
+        <v>17.33870967741936</v>
       </c>
       <c r="G12" t="n">
-        <v>147.04285</v>
+        <v>145.8716107142857</v>
       </c>
       <c r="H12" t="n">
-        <v>5.088075</v>
+        <v>5.620975</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2898193548387097</v>
+        <v>0.48365</v>
       </c>
       <c r="J12" t="n">
-        <v>612.8190999999999</v>
+        <v>614.5379785714285</v>
       </c>
       <c r="K12" t="n">
-        <v>107.86175</v>
+        <v>255.8227928571429</v>
       </c>
       <c r="L12" t="n">
-        <v>938.3424255663281</v>
+        <v>920.7545315996058</v>
       </c>
       <c r="M12" t="n">
-        <v>11.08433734939759</v>
+        <v>51.99004975124378</v>
       </c>
       <c r="N12" t="n">
-        <v>9.066666666666666</v>
+        <v>13.02752293577982</v>
       </c>
       <c r="O12" t="n">
-        <v>-242.865476035078</v>
+        <v>129.2512119896803</v>
       </c>
       <c r="P12" t="n">
-        <v>85.03335422330147</v>
+        <v>70.60726985233414</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.531189914880799</v>
+        <v>1.498287434960515</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>25.09153793098832</v>
+        <v>23.08788559719676</v>
       </c>
       <c r="E13" t="n">
-        <v>16.24491377543634</v>
+        <v>13.24023995894731</v>
       </c>
       <c r="F13" t="n">
-        <v>17.74193548387097</v>
+        <v>23.25268817204301</v>
       </c>
       <c r="G13" t="n">
-        <v>161.449425</v>
+        <v>206.057325</v>
       </c>
       <c r="H13" t="n">
-        <v>5.373699999999999</v>
+        <v>5.734375</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3577832661290323</v>
+        <v>0.4758362471198158</v>
       </c>
       <c r="J13" t="n">
-        <v>600.0540749999999</v>
+        <v>570.1100285714285</v>
       </c>
       <c r="K13" t="n">
-        <v>140.973625</v>
+        <v>181.1544464285714</v>
       </c>
       <c r="L13" t="n">
-        <v>952.7621807664843</v>
+        <v>942.8942145216629</v>
       </c>
       <c r="M13" t="n">
-        <v>12.07729468599034</v>
+        <v>33.16708229426434</v>
       </c>
       <c r="N13" t="n">
-        <v>5.54089709762533</v>
+        <v>7.67590618336887</v>
       </c>
       <c r="O13" t="n">
-        <v>65.41590287101565</v>
+        <v>-50.71177951362733</v>
       </c>
       <c r="P13" t="n">
-        <v>80.9759304544216</v>
+        <v>75.88672798236981</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.587793868021785</v>
+        <v>1.653881123411125</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>27.64309252820001</v>
+        <v>27.96157228985714</v>
       </c>
       <c r="E14" t="n">
-        <v>2.336773914466162</v>
+        <v>1.727505975039728</v>
       </c>
       <c r="F14" t="n">
         <v>0.1388888888888889</v>
@@ -1375,16 +1375,16 @@
         <v>0.6039249999999994</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4413576475694444</v>
+        <v>0.4505403298611111</v>
       </c>
       <c r="J14" t="n">
         <v>8.335825</v>
       </c>
       <c r="K14" t="n">
-        <v>317.17358125</v>
+        <v>323.7851125</v>
       </c>
       <c r="L14" t="n">
-        <v>458.6090682438653</v>
+        <v>488.8222426560772</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
@@ -1393,25 +1393,25 @@
         <v>0.1388888888888889</v>
       </c>
       <c r="O14" t="n">
-        <v>509.3767791075272</v>
+        <v>518.0651541781278</v>
       </c>
       <c r="P14" t="n">
-        <v>2.560855336265724</v>
+        <v>2.509876391036022</v>
       </c>
       <c r="Q14" t="n">
-        <v>55.01663821443772</v>
+        <v>58.64113541923891</v>
       </c>
       <c r="S14" t="n">
-        <v>26.29919999822252</v>
+        <v>26.8333719124581</v>
       </c>
       <c r="T14" t="n">
         <v>0.4166666666666667</v>
       </c>
       <c r="U14" t="n">
-        <v>325.50940625</v>
+        <v>332.1209375</v>
       </c>
       <c r="V14" t="n">
-        <v>3.404486871107124</v>
+        <v>3.33671375355551</v>
       </c>
     </row>
     <row r="15">
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>27.64014026720212</v>
+        <v>28.02829093160415</v>
       </c>
       <c r="E15" t="n">
-        <v>2.657309430178099</v>
+        <v>1.281999548793387</v>
       </c>
       <c r="F15" t="n">
         <v>0.1388888888888889</v>
@@ -1444,16 +1444,16 @@
         <v>0.6039249999999994</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4373069097222222</v>
+        <v>0.457785390625</v>
       </c>
       <c r="J15" t="n">
         <v>8.335825</v>
       </c>
       <c r="K15" t="n">
-        <v>314.25705</v>
+        <v>329.00155625</v>
       </c>
       <c r="L15" t="n">
-        <v>461.2973873188162</v>
+        <v>500.5611101230199</v>
       </c>
       <c r="M15" t="n">
         <v>100</v>
@@ -1462,25 +1462,25 @@
         <v>0.1388888888888889</v>
       </c>
       <c r="O15" t="n">
-        <v>516.8373340612964</v>
+        <v>527.2757779268102</v>
       </c>
       <c r="P15" t="n">
-        <v>2.584007783804897</v>
+        <v>2.471064715422788</v>
       </c>
       <c r="Q15" t="n">
-        <v>55.3391400753754</v>
+        <v>60.04937845060567</v>
       </c>
       <c r="S15" t="n">
-        <v>26.06356183486355</v>
+        <v>27.25482915709258</v>
       </c>
       <c r="T15" t="n">
         <v>0.4166666666666667</v>
       </c>
       <c r="U15" t="n">
-        <v>322.592875</v>
+        <v>337.33738125</v>
       </c>
       <c r="V15" t="n">
-        <v>3.435266510458422</v>
+        <v>3.285116211828066</v>
       </c>
     </row>
     <row r="16">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>27.92207505048732</v>
+        <v>28.05552052333226</v>
       </c>
       <c r="E16" t="n">
-        <v>3.021453144391929</v>
+        <v>1.310222435570517</v>
       </c>
       <c r="F16" t="n">
         <v>0.1388888888888889</v>
@@ -1513,16 +1513,16 @@
         <v>0.6039249999999994</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4411303211805555</v>
+        <v>0.4578945920138889</v>
       </c>
       <c r="J16" t="n">
         <v>8.335825</v>
       </c>
       <c r="K16" t="n">
-        <v>317.00990625</v>
+        <v>329.08018125</v>
       </c>
       <c r="L16" t="n">
-        <v>460.9186732987057</v>
+        <v>500.7786435973168</v>
       </c>
       <c r="M16" t="n">
         <v>100</v>
@@ -1531,25 +1531,25 @@
         <v>0.1388888888888889</v>
       </c>
       <c r="O16" t="n">
-        <v>515.6282567169831</v>
+        <v>527.4377235868881</v>
       </c>
       <c r="P16" t="n">
-        <v>2.562143651915519</v>
+        <v>2.470488905562997</v>
       </c>
       <c r="Q16" t="n">
-        <v>55.29370797715951</v>
+        <v>60.07547466475326</v>
       </c>
       <c r="S16" t="n">
-        <v>26.2859760437774</v>
+        <v>27.26118158365893</v>
       </c>
       <c r="T16" t="n">
         <v>0.4166666666666667</v>
       </c>
       <c r="U16" t="n">
-        <v>325.34573125</v>
+        <v>337.41600625</v>
       </c>
       <c r="V16" t="n">
-        <v>3.406199601089741</v>
+        <v>3.284350710911184</v>
       </c>
     </row>
     <row r="17">
@@ -1567,46 +1567,46 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.027996114971929</v>
+        <v>2.20024928384126</v>
       </c>
       <c r="E17" t="n">
-        <v>1.729621100788614</v>
+        <v>1.936029020594409</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="G17" t="n">
-        <v>1.88325</v>
+        <v>5.585700000000004</v>
       </c>
       <c r="H17" t="n">
-        <v>1.88325</v>
+        <v>2.392100000000003</v>
       </c>
       <c r="I17" t="n">
-        <v>0.004785000000000004</v>
+        <v>0.00984409722222223</v>
       </c>
       <c r="J17" t="n">
-        <v>7.0565</v>
+        <v>5.725514285714286</v>
       </c>
       <c r="K17" t="n">
-        <v>3.06195</v>
+        <v>4.456585714285713</v>
       </c>
       <c r="L17" t="n">
-        <v>9.46906425640625</v>
+        <v>11.22510128164062</v>
       </c>
       <c r="M17" t="n">
-        <v>1.955307262569832</v>
+        <v>10.06993006993007</v>
       </c>
       <c r="N17" t="n">
-        <v>72.22222222222223</v>
+        <v>86.84210526315789</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.00774495640625</v>
+        <v>-6.181609834319198</v>
       </c>
       <c r="P17" t="n">
-        <v>69.73894222929401</v>
+        <v>56.231173193293</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.341892475930879</v>
+        <v>1.96054026267096</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1627,46 +1627,46 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.736635388805798</v>
+        <v>4.746531400428134</v>
       </c>
       <c r="E18" t="n">
-        <v>1.577819494704957</v>
+        <v>3.437988746186372</v>
       </c>
       <c r="F18" t="n">
         <v>0.1388888888888889</v>
       </c>
       <c r="G18" t="n">
-        <v>2.274950000000002</v>
+        <v>1.369100000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>2.274950000000002</v>
+        <v>1.369100000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.005032847222222224</v>
+        <v>0.01344427083333333</v>
       </c>
       <c r="J18" t="n">
-        <v>6.6648</v>
+        <v>8.287200000000002</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3487</v>
+        <v>14.810775</v>
       </c>
       <c r="L18" t="n">
-        <v>15.12775496554687</v>
+        <v>38.87885555835936</v>
       </c>
       <c r="M18" t="n">
-        <v>10.47486033519553</v>
+        <v>21.81818181818182</v>
       </c>
       <c r="N18" t="n">
-        <v>91.13924050632912</v>
+        <v>88.81987577639751</v>
       </c>
       <c r="O18" t="n">
-        <v>-8.128330940546871</v>
+        <v>-20.38810342710937</v>
       </c>
       <c r="P18" t="n">
-        <v>73.94241970377766</v>
+        <v>35.87846986586487</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.269798788492809</v>
+        <v>4.691434448107847</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1687,46 +1687,46 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.4471107151105</v>
+        <v>2.796483165151353</v>
       </c>
       <c r="E19" t="n">
-        <v>1.943978327130965</v>
+        <v>1.586996063604083</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="G19" t="n">
-        <v>1.939175000000001</v>
+        <v>2.793824999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>1.939175000000001</v>
+        <v>1.995100000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.012138125</v>
+        <v>0.009519375</v>
       </c>
       <c r="J19" t="n">
-        <v>7.000575</v>
+        <v>8.026799999999998</v>
       </c>
       <c r="K19" t="n">
-        <v>9.300274999999999</v>
+        <v>8.060124999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>52.50094775320312</v>
+        <v>15.40481776601562</v>
       </c>
       <c r="M19" t="n">
-        <v>15.36312849162011</v>
+        <v>13.98601398601399</v>
       </c>
       <c r="N19" t="n">
-        <v>92.10526315789474</v>
+        <v>89.52380952380952</v>
       </c>
       <c r="O19" t="n">
-        <v>2.66610774054687</v>
+        <v>-6.565055328515625</v>
       </c>
       <c r="P19" t="n">
-        <v>42.94607336427242</v>
+        <v>49.89642209434059</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.499519361367191</v>
+        <v>1.919172991231328</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -1750,7 +1750,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.33297570248468</v>
+        <v>26.40664011058466</v>
       </c>
       <c r="E2" t="n">
-        <v>0.127590497538655</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.519300061463965</v>
+        <v>1.330843557915751</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3391062599062609</v>
+        <v>0.2244784792943265</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.74551971326165</v>
+        <v>23.70071684587813</v>
       </c>
       <c r="E4" t="n">
         <v>0.07760084263301543</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>285.2286375</v>
+        <v>283.9139125000001</v>
       </c>
       <c r="E5" t="n">
-        <v>2.457744517805819</v>
+        <v>0.2138113383298706</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8.179408333333333</v>
+        <v>8.153524999999998</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0448312484025756</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.092688760080645</v>
+        <v>1.102911410730287</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01642547009880324</v>
+        <v>0.01013193147701493</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>738.1008624999999</v>
+        <v>739.4155875</v>
       </c>
       <c r="E8" t="n">
-        <v>2.457744517805806</v>
+        <v>0.2138113383299514</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>527.7318</v>
+        <v>536.6521770833333</v>
       </c>
       <c r="E9" t="n">
-        <v>14.66655985018912</v>
+        <v>7.713742692769054</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1838.771662173942</v>
+        <v>1865.425893084316</v>
       </c>
       <c r="E10" t="n">
-        <v>75.52920381698871</v>
+        <v>18.79833108416747</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2224.535588973821</v>
+        <v>2323.961626184869</v>
       </c>
       <c r="E13" t="n">
-        <v>68.28042643061396</v>
+        <v>33.24664465069861</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>58.31491780914336</v>
+        <v>57.94627755022685</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5997374872401745</v>
+        <v>0.3457199771835254</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2.491011809340709</v>
+        <v>2.52283431571561</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09425177951408351</v>
+        <v>0.02483044523105024</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25.61201096039528</v>
+        <v>25.81910116631664</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3463123179751297</v>
+        <v>0.1596655604802483</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>22.08781362007168</v>
+        <v>22.1326164874552</v>
       </c>
       <c r="E17" t="n">
         <v>0.07760084263301747</v>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1265.8326625</v>
+        <v>1276.067764583333</v>
       </c>
       <c r="E18" t="n">
-        <v>17.1159322162119</v>
+        <v>7.891214861839402</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>71.31958189381237</v>
+        <v>71.03655021313833</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5713045839526912</v>
+        <v>0.3595717270490047</v>
       </c>
       <c r="F19" t="n">
         <v>3</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>26.1885230265213</v>
+        <v>24.18230350802262</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4536778733862379</v>
+        <v>2.315927922664013</v>
       </c>
       <c r="F20" t="n">
         <v>3</v>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16.74467301592618</v>
+        <v>14.07099631786412</v>
       </c>
       <c r="E21" t="n">
-        <v>0.266848321202234</v>
+        <v>1.895708518046851</v>
       </c>
       <c r="F21" t="n">
         <v>3</v>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25.89605734767025</v>
+        <v>28.00179211469534</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9149004416067268</v>
+        <v>2.172823593724394</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>261.175275</v>
+        <v>299.3728488095239</v>
       </c>
       <c r="E23" t="n">
-        <v>2.444604338129176</v>
+        <v>46.45060891646699</v>
       </c>
       <c r="F23" t="n">
         <v>3</v>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8.310175000000001</v>
+        <v>8.761416666666667</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6444936127495761</v>
+        <v>0.8784002897075642</v>
       </c>
       <c r="F24" t="n">
         <v>3</v>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.4380416218637992</v>
+        <v>0.5565292498719918</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03167233934136768</v>
+        <v>0.03854299097266502</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>721.3170416666666</v>
+        <v>695.38595</v>
       </c>
       <c r="E26" t="n">
-        <v>5.154823259356966</v>
+        <v>44.69009236862371</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>109.3853166666667</v>
+        <v>158.3177595238095</v>
       </c>
       <c r="E27" t="n">
-        <v>27.21940574967072</v>
+        <v>23.34615305766656</v>
       </c>
       <c r="F27" t="n">
         <v>3</v>
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1296.375863086839</v>
+        <v>1241.500763556972</v>
       </c>
       <c r="E28" t="n">
-        <v>156.3826252627279</v>
+        <v>215.9486229788413</v>
       </c>
       <c r="F28" t="n">
         <v>3</v>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.18288194869846</v>
+        <v>39.90134046571293</v>
       </c>
       <c r="E29" t="n">
-        <v>8.550357434862615</v>
+        <v>7.554054891388144</v>
       </c>
       <c r="F29" t="n">
         <v>3</v>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5.651906943923383</v>
+        <v>8.998389508024397</v>
       </c>
       <c r="E30" t="n">
-        <v>3.213286325077505</v>
+        <v>3.218974388282015</v>
       </c>
       <c r="F30" t="n">
         <v>3</v>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-119.7093686879824</v>
+        <v>-2.41217678679133</v>
       </c>
       <c r="E31" t="n">
-        <v>169.3954617318301</v>
+        <v>127.9470506369828</v>
       </c>
       <c r="F31" t="n">
         <v>3</v>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>86.88816491365411</v>
+        <v>81.50513221066738</v>
       </c>
       <c r="E32" t="n">
-        <v>2.844891732704328</v>
+        <v>1.643304254865415</v>
       </c>
       <c r="F32" t="n">
         <v>3</v>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1.796497770520399</v>
+        <v>1.792304528389497</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2074803767167312</v>
+        <v>0.3491388729196391</v>
       </c>
       <c r="F33" t="n">
         <v>3</v>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>1.527525231651947</v>
       </c>
       <c r="F34" t="n">
         <v>3</v>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>24.17192044391768</v>
+        <v>24.27485485847447</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1782876358597066</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>3</v>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-1.182461181959481</v>
+        <v>-1.345187212637706</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3183920969205906</v>
+        <v>0.250123308339837</v>
       </c>
       <c r="F36" t="n">
         <v>3</v>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>16.4426523297491</v>
+        <v>16.26344086021505</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3104033705320576</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>3</v>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>188.5771333333333</v>
+        <v>186.812075</v>
       </c>
       <c r="E38" t="n">
-        <v>2.528581770667209</v>
+        <v>0.04513352585661034</v>
       </c>
       <c r="F38" t="n">
         <v>3</v>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6.630112499999999</v>
+        <v>6.602374999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0480427592749413</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>3</v>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1.091140742607527</v>
+        <v>1.099658747759857</v>
       </c>
       <c r="E40" t="n">
-        <v>0.01896453145771046</v>
+        <v>0.01177129531145826</v>
       </c>
       <c r="F40" t="n">
         <v>3</v>
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>609.0078666666666</v>
+        <v>610.7729250000001</v>
       </c>
       <c r="E41" t="n">
-        <v>2.528581770667142</v>
+        <v>0.0451335258565958</v>
       </c>
       <c r="F41" t="n">
         <v>3</v>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>623.2315791666666</v>
+        <v>631.3340333333333</v>
       </c>
       <c r="E42" t="n">
-        <v>16.59563381548259</v>
+        <v>8.75581690384211</v>
       </c>
       <c r="F42" t="n">
         <v>3</v>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2173.061849247566</v>
+        <v>2229.278683266341</v>
       </c>
       <c r="E43" t="n">
-        <v>89.04201667790794</v>
+        <v>23.95617066266183</v>
       </c>
       <c r="F43" t="n">
         <v>3</v>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1048.818176447226</v>
+        <v>1070.863811896159</v>
       </c>
       <c r="E46" t="n">
-        <v>48.49010359926954</v>
+        <v>17.5451841250328</v>
       </c>
       <c r="F46" t="n">
         <v>3</v>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>49.42871587296251</v>
+        <v>49.17396501204887</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5684828700705817</v>
+        <v>0.3481350205221764</v>
       </c>
       <c r="F47" t="n">
         <v>3</v>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3.567837628096528</v>
+        <v>3.649930514995936</v>
       </c>
       <c r="E48" t="n">
-        <v>0.131801442555127</v>
+        <v>0.03923392199351299</v>
       </c>
       <c r="F48" t="n">
         <v>3</v>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>25.54088313934567</v>
+        <v>25.74540912209255</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3957412101854886</v>
+        <v>0.1814464404663031</v>
       </c>
       <c r="F49" t="n">
         <v>3</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>28.58422939068101</v>
+        <v>28.76344086021506</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3104033705320556</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>3</v>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1232.239445833333</v>
+        <v>1242.106958333334</v>
       </c>
       <c r="E51" t="n">
-        <v>19.09283742742422</v>
+        <v>8.754022326823716</v>
       </c>
       <c r="F51" t="n">
         <v>3</v>
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>66.76922892384259</v>
+        <v>66.48290839294668</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4850512999744201</v>
+        <v>0.300625115787693</v>
       </c>
       <c r="F52" t="n">
         <v>3</v>
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>25.27842843144478</v>
+        <v>23.77411587789459</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9143795596024932</v>
+        <v>3.241139502691634</v>
       </c>
       <c r="F53" t="n">
         <v>3</v>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>16.59190560576627</v>
+        <v>13.6164395347943</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9941131067525699</v>
+        <v>2.398986735508917</v>
       </c>
       <c r="F54" t="n">
         <v>3</v>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>19.75806451612904</v>
+        <v>20.3405017921147</v>
       </c>
       <c r="E55" t="n">
-        <v>2.16310173917084</v>
+        <v>2.958007319040151</v>
       </c>
       <c r="F55" t="n">
         <v>3</v>
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>167.5812916666667</v>
+        <v>191.0160702380952</v>
       </c>
       <c r="E56" t="n">
-        <v>24.19434563599441</v>
+        <v>39.81497524453936</v>
       </c>
       <c r="F56" t="n">
         <v>3</v>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>5.266866666666666</v>
+        <v>5.786591666666666</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1558169164703666</v>
+        <v>0.1969858137870178</v>
       </c>
       <c r="F57" t="n">
         <v>3</v>
@@ -3260,10 +3260,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.3347452620967743</v>
+        <v>0.4880109350998465</v>
       </c>
       <c r="E58" t="n">
-        <v>0.03891122640301144</v>
+        <v>0.01484364532377308</v>
       </c>
       <c r="F58" t="n">
         <v>3</v>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>597.2151916666667</v>
+        <v>575.5614476190475</v>
       </c>
       <c r="E59" t="n">
-        <v>17.19996770804259</v>
+        <v>36.55694915430898</v>
       </c>
       <c r="F59" t="n">
         <v>3</v>
@@ -3312,10 +3312,10 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>115.1293666666667</v>
+        <v>211.3942869047619</v>
       </c>
       <c r="E60" t="n">
-        <v>23.0850119820785</v>
+        <v>39.30431478337616</v>
       </c>
       <c r="F60" t="n">
         <v>3</v>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>874.8365826176823</v>
+        <v>879.3831945371639</v>
       </c>
       <c r="E61" t="n">
-        <v>122.6952392441686</v>
+        <v>91.50285790489707</v>
       </c>
       <c r="F61" t="n">
         <v>3</v>
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>8.20363579923559</v>
+        <v>46.46904401516937</v>
       </c>
       <c r="E62" t="n">
-        <v>5.870479516352392</v>
+        <v>11.57512345506649</v>
       </c>
       <c r="F62" t="n">
         <v>3</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5.366700359241611</v>
+        <v>12.39631212184183</v>
       </c>
       <c r="E63" t="n">
-        <v>3.790068237199328</v>
+        <v>4.438590771975025</v>
       </c>
       <c r="F63" t="n">
         <v>3</v>
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-8.467425101015579</v>
+        <v>-0.4156999148424347</v>
       </c>
       <c r="E64" t="n">
-        <v>207.564651038523</v>
+        <v>113.2319139791608</v>
       </c>
       <c r="F64" t="n">
         <v>3</v>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>83.90402125501843</v>
+        <v>73.27242078650671</v>
       </c>
       <c r="E65" t="n">
-        <v>2.557795772643011</v>
+        <v>2.64009627684179</v>
       </c>
       <c r="F65" t="n">
         <v>3</v>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1.462052481604077</v>
+        <v>1.527013700506257</v>
       </c>
       <c r="E66" t="n">
-        <v>0.171126612927147</v>
+        <v>0.1152220206699136</v>
       </c>
       <c r="F66" t="n">
         <v>3</v>
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>2.081665999466133</v>
       </c>
       <c r="F67" t="n">
         <v>3</v>
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>27.73510261529648</v>
+        <v>28.01512791493118</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1619296069350606</v>
+        <v>0.04833752578715014</v>
       </c>
       <c r="F68" t="n">
         <v>3</v>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2.671845496345397</v>
+        <v>1.439909319801211</v>
       </c>
       <c r="E69" t="n">
-        <v>0.3425709924784209</v>
+        <v>0.2494654483346253</v>
       </c>
       <c r="F69" t="n">
         <v>3</v>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.4399316261574073</v>
+        <v>0.4554067708333333</v>
       </c>
       <c r="E73" t="n">
-        <v>0.002275911157233448</v>
+        <v>0.00421481518431429</v>
       </c>
       <c r="F73" t="n">
         <v>3</v>
@@ -3702,10 +3702,10 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>316.1468458333333</v>
+        <v>327.28895</v>
       </c>
       <c r="E75" t="n">
-        <v>1.638656033208081</v>
+        <v>3.034666932706274</v>
       </c>
       <c r="F75" t="n">
         <v>3</v>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>460.2750429537957</v>
+        <v>496.7206654588046</v>
       </c>
       <c r="E76" t="n">
-        <v>1.455149434887337</v>
+        <v>6.841099493582388</v>
       </c>
       <c r="F76" t="n">
         <v>3</v>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>513.9474566286023</v>
+        <v>524.2595518972754</v>
       </c>
       <c r="E79" t="n">
-        <v>4.004221117443201</v>
+        <v>5.365116860464414</v>
       </c>
       <c r="F79" t="n">
         <v>3</v>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2.569002257328714</v>
+        <v>2.483810004007269</v>
       </c>
       <c r="E80" t="n">
-        <v>0.01301112246979353</v>
+        <v>0.02257598920973822</v>
       </c>
       <c r="F80" t="n">
         <v>3</v>
@@ -3858,10 +3858,10 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>55.21649542232421</v>
+        <v>59.58866284486595</v>
       </c>
       <c r="E81" t="n">
-        <v>0.1745657370311018</v>
+        <v>0.8206865539502656</v>
       </c>
       <c r="F81" t="n">
         <v>3</v>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>26.21624595895449</v>
+        <v>27.1164608844032</v>
       </c>
       <c r="E82" t="n">
-        <v>0.1323935404574366</v>
+        <v>0.2451828151778211</v>
       </c>
       <c r="F82" t="n">
         <v>3</v>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>324.4826708333333</v>
+        <v>335.624775</v>
       </c>
       <c r="E84" t="n">
-        <v>1.638656033208081</v>
+        <v>3.034666932706274</v>
       </c>
       <c r="F84" t="n">
         <v>3</v>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3.415317660885096</v>
+        <v>3.302060225431587</v>
       </c>
       <c r="E85" t="n">
-        <v>0.01729742207592626</v>
+        <v>0.03001327633714944</v>
       </c>
       <c r="F85" t="n">
         <v>3</v>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3.070580739629408</v>
+        <v>3.247754616473582</v>
       </c>
       <c r="E86" t="n">
-        <v>0.3571468675697115</v>
+        <v>1.331774228762663</v>
       </c>
       <c r="F86" t="n">
         <v>3</v>
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1.750472974208179</v>
+        <v>2.320337943461622</v>
       </c>
       <c r="E87" t="n">
-        <v>0.1839678589040039</v>
+        <v>0.9835209651501143</v>
       </c>
       <c r="F87" t="n">
         <v>3</v>
@@ -4040,10 +4040,10 @@
         </is>
       </c>
       <c r="D88" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="E88" t="n">
         <v>0.1388888888888889</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0</v>
       </c>
       <c r="F88" t="n">
         <v>3</v>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2.032458333333334</v>
+        <v>3.249541666666668</v>
       </c>
       <c r="E89" t="n">
-        <v>0.2118573994656162</v>
+        <v>2.144921245689067</v>
       </c>
       <c r="F89" t="n">
         <v>3</v>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2.032458333333334</v>
+        <v>1.918766666666668</v>
       </c>
       <c r="E90" t="n">
-        <v>0.2118573994656162</v>
+        <v>0.515754140393787</v>
       </c>
       <c r="F90" t="n">
         <v>3</v>
@@ -4118,10 +4118,10 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.007318657407407409</v>
+        <v>0.01093591435185185</v>
       </c>
       <c r="E91" t="n">
-        <v>0.004175620668646576</v>
+        <v>0.002178359545401961</v>
       </c>
       <c r="F91" t="n">
         <v>3</v>
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>6.907291666666667</v>
+        <v>7.346504761904762</v>
       </c>
       <c r="E92" t="n">
-        <v>0.2118573994656156</v>
+        <v>1.409843832814532</v>
       </c>
       <c r="F92" t="n">
         <v>3</v>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>4.903641666666666</v>
+        <v>9.109161904761903</v>
       </c>
       <c r="E93" t="n">
-        <v>3.824260698678678</v>
+        <v>5.256202789254279</v>
       </c>
       <c r="F93" t="n">
         <v>3</v>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>25.69925565838541</v>
+        <v>21.8362582020052</v>
       </c>
       <c r="E94" t="n">
-        <v>23.38275474563442</v>
+        <v>14.90654557436251</v>
       </c>
       <c r="F94" t="n">
         <v>3</v>
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>9.264432029795158</v>
+        <v>15.29137529137529</v>
       </c>
       <c r="E95" t="n">
-        <v>6.785371768696881</v>
+        <v>5.981916991084547</v>
       </c>
       <c r="F95" t="n">
         <v>3</v>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>85.15557529548202</v>
+        <v>88.39526352112163</v>
       </c>
       <c r="E96" t="n">
-        <v>11.2110220867249</v>
+        <v>1.390361863292114</v>
       </c>
       <c r="F96" t="n">
         <v>3</v>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>-2.823322718802083</v>
+        <v>-11.04492286331473</v>
       </c>
       <c r="E97" t="n">
-        <v>5.399581954305851</v>
+        <v>8.093702792758537</v>
       </c>
       <c r="F97" t="n">
         <v>3</v>
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>62.2091450991147</v>
+        <v>47.33535505116615</v>
       </c>
       <c r="E98" t="n">
-        <v>16.8141831563678</v>
+        <v>10.41524994819144</v>
       </c>
       <c r="F98" t="n">
         <v>3</v>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3.703736875263626</v>
+        <v>2.857049234003378</v>
       </c>
       <c r="E99" t="n">
-        <v>3.319823194476023</v>
+        <v>1.588758838867754</v>
       </c>
       <c r="F99" t="n">
         <v>3</v>
@@ -4379,7 +4379,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -4422,13 +4422,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.182461181959481</v>
+        <v>-1.345187212637706</v>
       </c>
       <c r="D2" t="n">
-        <v>16.59190560576627</v>
+        <v>13.6164395347943</v>
       </c>
       <c r="E2" t="n">
-        <v>17.77436678772575</v>
+        <v>14.96162674743201</v>
       </c>
     </row>
     <row r="3">
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.58422939068101</v>
+        <v>28.76344086021506</v>
       </c>
     </row>
     <row r="4">
@@ -4458,13 +4458,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>188.5771333333333</v>
+        <v>186.812075</v>
       </c>
       <c r="D4" t="n">
-        <v>167.5812916666667</v>
+        <v>191.0160702380952</v>
       </c>
       <c r="E4" t="n">
-        <v>-20.99584166666662</v>
+        <v>4.203995238095274</v>
       </c>
     </row>
     <row r="5">
@@ -4479,13 +4479,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>623.2315791666666</v>
+        <v>631.3340333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>115.1293666666667</v>
+        <v>211.3942869047619</v>
       </c>
       <c r="E5" t="n">
-        <v>-508.1022125</v>
+        <v>-419.9397464285714</v>
       </c>
     </row>
     <row r="6">
@@ -4500,13 +4500,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.091140742607527</v>
+        <v>1.099658747759857</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3347452620967743</v>
+        <v>0.4880109350998465</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7563954805107524</v>
+        <v>-0.61164781266001</v>
       </c>
     </row>
     <row r="7">
@@ -4521,13 +4521,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2173.061849247566</v>
+        <v>2229.278683266341</v>
       </c>
       <c r="D7" t="n">
-        <v>874.8365826176823</v>
+        <v>879.3831945371639</v>
       </c>
       <c r="E7" t="n">
-        <v>-1298.225266629883</v>
+        <v>-1349.895488729177</v>
       </c>
     </row>
     <row r="8">
@@ -4542,13 +4542,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.630112499999999</v>
+        <v>6.602374999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>5.266866666666666</v>
+        <v>5.786591666666666</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.363245833333333</v>
+        <v>-0.8157833333333331</v>
       </c>
     </row>
     <row r="9">
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25.54088313934567</v>
+        <v>25.74540912209255</v>
       </c>
     </row>
     <row r="10">
@@ -4578,13 +4578,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1048.818176447226</v>
+        <v>1070.863811896159</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.467425101015579</v>
+        <v>-0.4156999148424347</v>
       </c>
       <c r="E10" t="n">
-        <v>-1057.285601548242</v>
+        <v>-1071.279511811001</v>
       </c>
     </row>
     <row r="11">
@@ -4602,10 +4602,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>5.366700359241611</v>
+        <v>12.39631212184183</v>
       </c>
       <c r="E11" t="n">
-        <v>5.366700359241611</v>
+        <v>12.39631212184183</v>
       </c>
     </row>
     <row r="12">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>66.76922892384259</v>
+        <v>66.48290839294668</v>
       </c>
     </row>
     <row r="13">
@@ -4635,13 +4635,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.567837628096528</v>
+        <v>3.649930514995936</v>
       </c>
       <c r="D13" t="n">
-        <v>1.462052481604077</v>
+        <v>1.527013700506257</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.105785146492451</v>
+        <v>-2.122916814489679</v>
       </c>
     </row>
     <row r="14">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24.17192044391768</v>
+        <v>24.27485485847447</v>
       </c>
       <c r="D14" t="n">
-        <v>25.27842843144478</v>
+        <v>23.77411587789459</v>
       </c>
       <c r="E14" t="n">
-        <v>1.106507987527095</v>
+        <v>-0.5007389805798823</v>
       </c>
     </row>
     <row r="15">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>6.333333333333333</v>
       </c>
     </row>
     <row r="16">
@@ -4692,13 +4692,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.4426523297491</v>
+        <v>16.26344086021505</v>
       </c>
       <c r="D16" t="n">
-        <v>19.75806451612904</v>
+        <v>20.3405017921147</v>
       </c>
       <c r="E16" t="n">
-        <v>3.315412186379938</v>
+        <v>4.077060931899648</v>
       </c>
     </row>
     <row r="17">
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1232.239445833333</v>
+        <v>1242.106958333334</v>
       </c>
     </row>
     <row r="18">
@@ -4731,10 +4731,10 @@
         <v>100</v>
       </c>
       <c r="D18" t="n">
-        <v>8.20363579923559</v>
+        <v>46.46904401516937</v>
       </c>
       <c r="E18" t="n">
-        <v>-91.79636420076442</v>
+        <v>-53.53095598483063</v>
       </c>
     </row>
     <row r="19">
@@ -4749,13 +4749,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>609.0078666666666</v>
+        <v>610.7729250000001</v>
       </c>
       <c r="D19" t="n">
-        <v>597.2151916666667</v>
+        <v>575.5614476190475</v>
       </c>
       <c r="E19" t="n">
-        <v>-11.79267499999992</v>
+        <v>-35.2114773809526</v>
       </c>
     </row>
     <row r="20">
@@ -4770,13 +4770,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>49.42871587296251</v>
+        <v>49.17396501204887</v>
       </c>
       <c r="D20" t="n">
-        <v>83.90402125501843</v>
+        <v>73.27242078650671</v>
       </c>
       <c r="E20" t="n">
-        <v>34.47530538205593</v>
+        <v>24.09845577445784</v>
       </c>
     </row>
     <row r="21">
@@ -4791,13 +4791,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.519300061463965</v>
+        <v>1.330843557915751</v>
       </c>
       <c r="D21" t="n">
-        <v>16.74467301592618</v>
+        <v>14.07099631786412</v>
       </c>
       <c r="E21" t="n">
-        <v>15.22537295446221</v>
+        <v>12.74015275994837</v>
       </c>
     </row>
     <row r="22">
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.08781362007168</v>
+        <v>22.1326164874552</v>
       </c>
     </row>
     <row r="23">
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>285.2286375</v>
+        <v>283.9139125000001</v>
       </c>
       <c r="D23" t="n">
-        <v>261.175275</v>
+        <v>299.3728488095239</v>
       </c>
       <c r="E23" t="n">
-        <v>-24.05336250000005</v>
+        <v>15.45893630952378</v>
       </c>
     </row>
     <row r="24">
@@ -4848,13 +4848,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>527.7318</v>
+        <v>536.6521770833333</v>
       </c>
       <c r="D24" t="n">
-        <v>109.3853166666667</v>
+        <v>158.3177595238095</v>
       </c>
       <c r="E24" t="n">
-        <v>-418.3464833333334</v>
+        <v>-378.3344175595238</v>
       </c>
     </row>
     <row r="25">
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.092688760080645</v>
+        <v>1.102911410730287</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4380416218637992</v>
+        <v>0.5565292498719918</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6546471382168457</v>
+        <v>-0.5463821608582948</v>
       </c>
     </row>
     <row r="26">
@@ -4890,13 +4890,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1838.771662173942</v>
+        <v>1865.425893084316</v>
       </c>
       <c r="D26" t="n">
-        <v>1296.375863086839</v>
+        <v>1241.500763556972</v>
       </c>
       <c r="E26" t="n">
-        <v>-542.3957990871031</v>
+        <v>-623.9251295273448</v>
       </c>
     </row>
     <row r="27">
@@ -4911,13 +4911,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8.179408333333333</v>
+        <v>8.153524999999998</v>
       </c>
       <c r="D27" t="n">
-        <v>8.310175000000001</v>
+        <v>8.761416666666667</v>
       </c>
       <c r="E27" t="n">
-        <v>0.130766666666668</v>
+        <v>0.6078916666666689</v>
       </c>
     </row>
     <row r="28">
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25.61201096039528</v>
+        <v>25.81910116631664</v>
       </c>
     </row>
     <row r="29">
@@ -4947,13 +4947,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2224.535588973821</v>
+        <v>2323.961626184869</v>
       </c>
       <c r="D29" t="n">
-        <v>-119.7093686879824</v>
+        <v>-2.41217678679133</v>
       </c>
       <c r="E29" t="n">
-        <v>-2344.244957661803</v>
+        <v>-2326.37380297166</v>
       </c>
     </row>
     <row r="30">
@@ -4971,10 +4971,10 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>5.651906943923383</v>
+        <v>8.998389508024397</v>
       </c>
       <c r="E30" t="n">
-        <v>5.651906943923383</v>
+        <v>8.998389508024397</v>
       </c>
     </row>
     <row r="31">
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>71.31958189381237</v>
+        <v>71.03655021313833</v>
       </c>
     </row>
     <row r="32">
@@ -5004,13 +5004,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2.491011809340709</v>
+        <v>2.52283431571561</v>
       </c>
       <c r="D32" t="n">
-        <v>1.796497770520399</v>
+        <v>1.792304528389497</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6945140388203093</v>
+        <v>-0.730529787326113</v>
       </c>
     </row>
     <row r="33">
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>26.33297570248468</v>
+        <v>26.40664011058466</v>
       </c>
       <c r="D33" t="n">
-        <v>26.1885230265213</v>
+        <v>24.18230350802262</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1444526759633789</v>
+        <v>-2.224336602562037</v>
       </c>
     </row>
     <row r="34">
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>11.66666666666667</v>
       </c>
     </row>
     <row r="35">
@@ -5061,13 +5061,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>23.74551971326165</v>
+        <v>23.70071684587813</v>
       </c>
       <c r="D35" t="n">
-        <v>25.89605734767025</v>
+        <v>28.00179211469534</v>
       </c>
       <c r="E35" t="n">
-        <v>2.150537634408604</v>
+        <v>4.301075268817204</v>
       </c>
     </row>
     <row r="36">
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1265.8326625</v>
+        <v>1276.067764583333</v>
       </c>
     </row>
     <row r="37">
@@ -5100,10 +5100,10 @@
         <v>100</v>
       </c>
       <c r="D37" t="n">
-        <v>11.18288194869846</v>
+        <v>39.90134046571293</v>
       </c>
       <c r="E37" t="n">
-        <v>-88.81711805130153</v>
+        <v>-60.09865953428707</v>
       </c>
     </row>
     <row r="38">
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>738.1008624999999</v>
+        <v>739.4155875</v>
       </c>
       <c r="D38" t="n">
-        <v>721.3170416666666</v>
+        <v>695.38595</v>
       </c>
       <c r="E38" t="n">
-        <v>-16.78382083333338</v>
+        <v>-44.02963750000004</v>
       </c>
     </row>
     <row r="39">
@@ -5139,13 +5139,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>58.31491780914336</v>
+        <v>57.94627755022685</v>
       </c>
       <c r="D39" t="n">
-        <v>86.88816491365411</v>
+        <v>81.50513221066738</v>
       </c>
       <c r="E39" t="n">
-        <v>28.57324710451075</v>
+        <v>23.55885466044054</v>
       </c>
     </row>
     <row r="40">
@@ -5160,13 +5160,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.671845496345397</v>
+        <v>1.439909319801211</v>
       </c>
       <c r="D40" t="n">
-        <v>1.750472974208179</v>
+        <v>2.320337943461622</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.921372522137218</v>
+        <v>0.8804286236604109</v>
       </c>
     </row>
     <row r="41">
@@ -5199,10 +5199,10 @@
         <v>0.6039249999999994</v>
       </c>
       <c r="D42" t="n">
-        <v>2.032458333333334</v>
+        <v>3.249541666666668</v>
       </c>
       <c r="E42" t="n">
-        <v>1.428533333333335</v>
+        <v>2.645616666666669</v>
       </c>
     </row>
     <row r="43">
@@ -5217,13 +5217,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>316.1468458333333</v>
+        <v>327.28895</v>
       </c>
       <c r="D43" t="n">
-        <v>4.903641666666666</v>
+        <v>9.109161904761903</v>
       </c>
       <c r="E43" t="n">
-        <v>-311.2432041666667</v>
+        <v>-318.1797880952381</v>
       </c>
     </row>
     <row r="44">
@@ -5238,13 +5238,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.4399316261574073</v>
+        <v>0.4554067708333333</v>
       </c>
       <c r="D44" t="n">
-        <v>0.007318657407407409</v>
+        <v>0.01093591435185185</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.4326129687499999</v>
+        <v>-0.4444708564814814</v>
       </c>
     </row>
     <row r="45">
@@ -5259,13 +5259,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>460.2750429537957</v>
+        <v>496.7206654588046</v>
       </c>
       <c r="D45" t="n">
-        <v>25.69925565838541</v>
+        <v>21.8362582020052</v>
       </c>
       <c r="E45" t="n">
-        <v>-434.5757872954103</v>
+        <v>-474.8844072567994</v>
       </c>
     </row>
     <row r="46">
@@ -5283,10 +5283,10 @@
         <v>0.6039249999999994</v>
       </c>
       <c r="D46" t="n">
-        <v>2.032458333333334</v>
+        <v>1.918766666666668</v>
       </c>
       <c r="E46" t="n">
-        <v>1.428533333333335</v>
+        <v>1.314841666666669</v>
       </c>
     </row>
     <row r="47">
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>26.21624595895449</v>
+        <v>27.1164608844032</v>
       </c>
     </row>
     <row r="48">
@@ -5316,13 +5316,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>513.9474566286023</v>
+        <v>524.2595518972754</v>
       </c>
       <c r="D48" t="n">
-        <v>-2.823322718802083</v>
+        <v>-11.04492286331473</v>
       </c>
       <c r="E48" t="n">
-        <v>-516.7707793474043</v>
+        <v>-535.3044747605901</v>
       </c>
     </row>
     <row r="49">
@@ -5340,10 +5340,10 @@
         <v>0.1388888888888889</v>
       </c>
       <c r="D49" t="n">
-        <v>85.15557529548202</v>
+        <v>88.39526352112163</v>
       </c>
       <c r="E49" t="n">
-        <v>85.01668640659314</v>
+        <v>88.25637463223275</v>
       </c>
     </row>
     <row r="50">
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3.415317660885096</v>
+        <v>3.302060225431587</v>
       </c>
     </row>
     <row r="51">
@@ -5373,13 +5373,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>55.21649542232421</v>
+        <v>59.58866284486595</v>
       </c>
       <c r="D51" t="n">
-        <v>3.703736875263626</v>
+        <v>2.857049234003378</v>
       </c>
       <c r="E51" t="n">
-        <v>-51.51275854706059</v>
+        <v>-56.73161361086257</v>
       </c>
     </row>
     <row r="52">
@@ -5394,13 +5394,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>27.73510261529648</v>
+        <v>28.01512791493118</v>
       </c>
       <c r="D52" t="n">
-        <v>3.070580739629408</v>
+        <v>3.247754616473582</v>
       </c>
       <c r="E52" t="n">
-        <v>-24.66452187566707</v>
+        <v>-24.7673732984576</v>
       </c>
     </row>
     <row r="53">
@@ -5433,10 +5433,10 @@
         <v>0.1388888888888889</v>
       </c>
       <c r="D54" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="E54" t="n">
         <v>0.1388888888888889</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>324.4826708333333</v>
+        <v>335.624775</v>
       </c>
     </row>
     <row r="56">
@@ -5469,10 +5469,10 @@
         <v>100</v>
       </c>
       <c r="D56" t="n">
-        <v>9.264432029795158</v>
+        <v>15.29137529137529</v>
       </c>
       <c r="E56" t="n">
-        <v>-90.73556797020484</v>
+        <v>-84.70862470862471</v>
       </c>
     </row>
     <row r="57">
@@ -5490,10 +5490,10 @@
         <v>8.335825</v>
       </c>
       <c r="D57" t="n">
-        <v>6.907291666666667</v>
+        <v>7.346504761904762</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.428533333333333</v>
+        <v>-0.9893202380952379</v>
       </c>
     </row>
     <row r="58">
@@ -5508,13 +5508,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2.569002257328714</v>
+        <v>2.483810004007269</v>
       </c>
       <c r="D58" t="n">
-        <v>62.2091450991147</v>
+        <v>47.33535505116615</v>
       </c>
       <c r="E58" t="n">
-        <v>59.64014284178599</v>
+        <v>44.85154504715889</v>
       </c>
     </row>
   </sheetData>
